--- a/examples/quick_test.xlsx
+++ b/examples/quick_test.xlsx
@@ -5710,10 +5710,10 @@
         <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>38.86</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3">
@@ -5721,13 +5721,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>38.86</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">
@@ -5924,7 +5924,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1203</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="3">
